--- a/streamlit_dashboard_monitoring/captured_data/with_ASCON/ppg_sensor_ascon_22.xlsx
+++ b/streamlit_dashboard_monitoring/captured_data/with_ASCON/ppg_sensor_ascon_22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H94"/>
+  <dimension ref="A1:M147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,2795 +469,6600 @@
           <t>Sensor_Status</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>CPU_Load_%</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Memory_Used_%</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Latency_ms</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Enc_Time_us</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Dec_Time_ms</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:05.873</t>
+          <t>2026-05-29 09:44:46.920</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1779505020890</v>
+        <v>1780022685767</v>
       </c>
       <c r="C2" t="n">
-        <v>92249</v>
+        <v>80651</v>
       </c>
       <c r="D2" t="n">
-        <v>-1045.72</v>
+        <v>-1370.23</v>
       </c>
       <c r="E2" t="n">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="F2" t="n">
-        <v>1952</v>
+        <v>1718</v>
       </c>
       <c r="G2" t="n">
-        <v>337.84</v>
+        <v>336.34</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I2" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J2" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1152</v>
+      </c>
+      <c r="L2" t="n">
+        <v>124</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:05.935</t>
+          <t>2026-05-29 09:44:46.921</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1779505021091</v>
+        <v>1780022685967</v>
       </c>
       <c r="C3" t="n">
-        <v>92483</v>
+        <v>79796</v>
       </c>
       <c r="D3" t="n">
-        <v>-759.4400000000001</v>
+        <v>-2156.72</v>
       </c>
       <c r="E3" t="n">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="F3" t="n">
-        <v>1952</v>
+        <v>9134</v>
       </c>
       <c r="G3" t="n">
-        <v>337.84</v>
+        <v>336.34</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I3" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J3" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K3" t="n">
+        <v>953</v>
+      </c>
+      <c r="L3" t="n">
+        <v>100</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.849</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:06.277</t>
+          <t>2026-05-29 09:44:47.503</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1779505021292</v>
+        <v>1780022686167</v>
       </c>
       <c r="C4" t="n">
-        <v>92187</v>
+        <v>79907</v>
       </c>
       <c r="D4" t="n">
-        <v>-1017.47</v>
+        <v>-1937.88</v>
       </c>
       <c r="E4" t="n">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="F4" t="n">
-        <v>1952</v>
+        <v>9134</v>
       </c>
       <c r="G4" t="n">
-        <v>337.84</v>
+        <v>336.34</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I4" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J4" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1335</v>
+      </c>
+      <c r="L4" t="n">
+        <v>117</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.227</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:06.293</t>
+          <t>2026-05-29 09:44:47.504</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1779505021493</v>
+        <v>1780022686367</v>
       </c>
       <c r="C5" t="n">
-        <v>92604</v>
+        <v>79829</v>
       </c>
       <c r="D5" t="n">
-        <v>-549.59</v>
+        <v>-1918.99</v>
       </c>
       <c r="E5" t="n">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="F5" t="n">
-        <v>1952</v>
+        <v>9134</v>
       </c>
       <c r="G5" t="n">
-        <v>337.84</v>
+        <v>336.34</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I5" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J5" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1136</v>
+      </c>
+      <c r="L5" t="n">
+        <v>114</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.989</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:06.308</t>
+          <t>2026-05-29 09:44:47.506</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1779505021695</v>
+        <v>1780022686567</v>
       </c>
       <c r="C6" t="n">
-        <v>92269</v>
+        <v>81032</v>
       </c>
       <c r="D6" t="n">
-        <v>-857.11</v>
+        <v>-620.04</v>
       </c>
       <c r="E6" t="n">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="F6" t="n">
-        <v>1871</v>
+        <v>9134</v>
       </c>
       <c r="G6" t="n">
-        <v>337.84</v>
+        <v>336.34</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I6" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J6" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K6" t="n">
+        <v>937</v>
+      </c>
+      <c r="L6" t="n">
+        <v>117</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.399</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:07.547</t>
+          <t>2026-05-29 09:44:47.726</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1779505021896</v>
+        <v>1780022686767</v>
       </c>
       <c r="C7" t="n">
-        <v>92216</v>
+        <v>81948</v>
       </c>
       <c r="D7" t="n">
-        <v>-867.26</v>
+        <v>326.96</v>
       </c>
       <c r="E7" t="n">
         <v>96</v>
       </c>
       <c r="F7" t="n">
-        <v>1871</v>
+        <v>760</v>
       </c>
       <c r="G7" t="n">
-        <v>337.84</v>
+        <v>339.7</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I7" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J7" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K7" t="n">
+        <v>958</v>
+      </c>
+      <c r="L7" t="n">
+        <v>107</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.261</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:07.568</t>
+          <t>2026-05-29 09:44:47.742</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1779505022097</v>
+        <v>1780022686967</v>
       </c>
       <c r="C8" t="n">
-        <v>92448</v>
+        <v>83214</v>
       </c>
       <c r="D8" t="n">
-        <v>-591.89</v>
+        <v>1576.61</v>
       </c>
       <c r="E8" t="n">
         <v>96</v>
       </c>
       <c r="F8" t="n">
-        <v>1871</v>
+        <v>760</v>
       </c>
       <c r="G8" t="n">
-        <v>337.84</v>
+        <v>339.7</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I8" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J8" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K8" t="n">
+        <v>774</v>
+      </c>
+      <c r="L8" t="n">
+        <v>113</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.344</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:07.614</t>
+          <t>2026-05-29 09:44:48.232</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1779505022298</v>
+        <v>1780022687186</v>
       </c>
       <c r="C9" t="n">
-        <v>92232</v>
+        <v>82845</v>
       </c>
       <c r="D9" t="n">
-        <v>-778.3</v>
+        <v>1128.78</v>
       </c>
       <c r="E9" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F9" t="n">
-        <v>624</v>
+        <v>760</v>
       </c>
       <c r="G9" t="n">
-        <v>344.71</v>
+        <v>339.7</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I9" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J9" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1045</v>
+      </c>
+      <c r="L9" t="n">
+        <v>111</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.705</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:07.619</t>
+          <t>2026-05-29 09:44:48.233</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1779505022499</v>
+        <v>1780022687386</v>
       </c>
       <c r="C10" t="n">
-        <v>92420</v>
+        <v>82934</v>
       </c>
       <c r="D10" t="n">
-        <v>-551.38</v>
+        <v>1161.34</v>
       </c>
       <c r="E10" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F10" t="n">
-        <v>624</v>
+        <v>760</v>
       </c>
       <c r="G10" t="n">
-        <v>344.71</v>
+        <v>339.7</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I10" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J10" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K10" t="n">
+        <v>846</v>
+      </c>
+      <c r="L10" t="n">
+        <v>105</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.085</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:08.206</t>
+          <t>2026-05-29 09:44:48.740</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1779505022701</v>
+        <v>1780022687586</v>
       </c>
       <c r="C11" t="n">
-        <v>92557</v>
+        <v>83003</v>
       </c>
       <c r="D11" t="n">
-        <v>-386.82</v>
+        <v>1172.28</v>
       </c>
       <c r="E11" t="n">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="F11" t="n">
-        <v>362</v>
+        <v>760</v>
       </c>
       <c r="G11" t="n">
-        <v>373.69</v>
+        <v>339.7</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I11" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J11" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1153</v>
+      </c>
+      <c r="L11" t="n">
+        <v>111</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:08.226</t>
+          <t>2026-05-29 09:44:48.742</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1779505022902</v>
+        <v>1780022687786</v>
       </c>
       <c r="C12" t="n">
-        <v>92696</v>
+        <v>82939</v>
       </c>
       <c r="D12" t="n">
-        <v>-228.47</v>
+        <v>1049.66</v>
       </c>
       <c r="E12" t="n">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="F12" t="n">
-        <v>362</v>
+        <v>760</v>
       </c>
       <c r="G12" t="n">
-        <v>373.69</v>
+        <v>339.7</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I12" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J12" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K12" t="n">
+        <v>955</v>
+      </c>
+      <c r="L12" t="n">
+        <v>106</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.289</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:08.228</t>
+          <t>2026-05-29 09:44:49.746</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1779505023103</v>
+        <v>1780022687986</v>
       </c>
       <c r="C13" t="n">
-        <v>92667</v>
+        <v>82757</v>
       </c>
       <c r="D13" t="n">
-        <v>-246.05</v>
+        <v>815.1799999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="F13" t="n">
-        <v>362</v>
+        <v>760</v>
       </c>
       <c r="G13" t="n">
-        <v>373.69</v>
+        <v>339.7</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I13" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J13" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1759</v>
+      </c>
+      <c r="L13" t="n">
+        <v>114</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.105</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:08.236</t>
+          <t>2026-05-29 09:44:49.747</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1779505023304</v>
+        <v>1780022688186</v>
       </c>
       <c r="C14" t="n">
-        <v>92768</v>
+        <v>82367</v>
       </c>
       <c r="D14" t="n">
-        <v>-132.75</v>
+        <v>384.42</v>
       </c>
       <c r="E14" t="n">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="F14" t="n">
-        <v>362</v>
+        <v>760</v>
       </c>
       <c r="G14" t="n">
-        <v>373.69</v>
+        <v>339.7</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I14" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J14" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1560</v>
+      </c>
+      <c r="L14" t="n">
+        <v>107</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.958</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:08.465</t>
+          <t>2026-05-29 09:44:49.749</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1779505023506</v>
+        <v>1780022688386</v>
       </c>
       <c r="C15" t="n">
-        <v>92579</v>
+        <v>82052</v>
       </c>
       <c r="D15" t="n">
-        <v>-315.11</v>
+        <v>50.2</v>
       </c>
       <c r="E15" t="n">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="F15" t="n">
-        <v>362</v>
+        <v>760</v>
       </c>
       <c r="G15" t="n">
-        <v>373.69</v>
+        <v>339.7</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I15" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J15" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1362</v>
+      </c>
+      <c r="L15" t="n">
+        <v>106</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.964</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:08.467</t>
+          <t>2026-05-29 09:44:49.750</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1779505023707</v>
+        <v>1780022688605</v>
       </c>
       <c r="C16" t="n">
-        <v>92665</v>
+        <v>82012</v>
       </c>
       <c r="D16" t="n">
-        <v>-213.36</v>
+        <v>7.69</v>
       </c>
       <c r="E16" t="n">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="F16" t="n">
-        <v>362</v>
+        <v>760</v>
       </c>
       <c r="G16" t="n">
-        <v>373.69</v>
+        <v>339.7</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I16" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J16" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1144</v>
+      </c>
+      <c r="L16" t="n">
+        <v>104</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.861</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:08.470</t>
+          <t>2026-05-29 09:44:50.172</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1779505023908</v>
+        <v>1780022688805</v>
       </c>
       <c r="C17" t="n">
-        <v>92503</v>
+        <v>82388</v>
       </c>
       <c r="D17" t="n">
-        <v>-364.69</v>
+        <v>383.3</v>
       </c>
       <c r="E17" t="n">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="F17" t="n">
-        <v>362</v>
+        <v>760</v>
       </c>
       <c r="G17" t="n">
-        <v>373.69</v>
+        <v>339.7</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I17" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J17" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1366</v>
+      </c>
+      <c r="L17" t="n">
+        <v>107</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.991</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:08.899</t>
+          <t>2026-05-29 09:44:50.174</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1779505024109</v>
+        <v>1780022689005</v>
       </c>
       <c r="C18" t="n">
-        <v>92568</v>
+        <v>81838</v>
       </c>
       <c r="D18" t="n">
-        <v>-281.45</v>
+        <v>-185.86</v>
       </c>
       <c r="E18" t="n">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="F18" t="n">
-        <v>362</v>
+        <v>760</v>
       </c>
       <c r="G18" t="n">
-        <v>373.69</v>
+        <v>339.7</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I18" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J18" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1168</v>
+      </c>
+      <c r="L18" t="n">
+        <v>120</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.121</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:08.923</t>
+          <t>2026-05-29 09:44:50.175</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1779505024311</v>
+        <v>1780022689205</v>
       </c>
       <c r="C19" t="n">
-        <v>92601</v>
+        <v>81881</v>
       </c>
       <c r="D19" t="n">
-        <v>-234.38</v>
+        <v>-133.57</v>
       </c>
       <c r="E19" t="n">
+        <v>96</v>
+      </c>
+      <c r="F19" t="n">
+        <v>760</v>
+      </c>
+      <c r="G19" t="n">
+        <v>339.7</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J19" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K19" t="n">
+        <v>969</v>
+      </c>
+      <c r="L19" t="n">
         <v>113</v>
       </c>
-      <c r="F19" t="n">
-        <v>362</v>
-      </c>
-      <c r="G19" t="n">
-        <v>373.69</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
+      <c r="M19" t="n">
+        <v>0.6889999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:08.929</t>
+          <t>2026-05-29 09:44:50.526</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1779505024512</v>
+        <v>1780022689405</v>
       </c>
       <c r="C20" t="n">
-        <v>92455</v>
+        <v>81892</v>
       </c>
       <c r="D20" t="n">
-        <v>-368.66</v>
+        <v>-115.89</v>
       </c>
       <c r="E20" t="n">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="F20" t="n">
-        <v>362</v>
+        <v>760</v>
       </c>
       <c r="G20" t="n">
-        <v>373.69</v>
+        <v>339.7</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I20" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J20" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1120</v>
+      </c>
+      <c r="L20" t="n">
+        <v>106</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.217</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:09.272</t>
+          <t>2026-05-29 09:44:50.528</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1779505024713</v>
+        <v>1780022689605</v>
       </c>
       <c r="C21" t="n">
-        <v>92546</v>
+        <v>81589</v>
       </c>
       <c r="D21" t="n">
-        <v>-259.23</v>
+        <v>-413.09</v>
       </c>
       <c r="E21" t="n">
+        <v>96</v>
+      </c>
+      <c r="F21" t="n">
+        <v>760</v>
+      </c>
+      <c r="G21" t="n">
+        <v>339.7</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J21" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K21" t="n">
+        <v>922</v>
+      </c>
+      <c r="L21" t="n">
         <v>113</v>
       </c>
-      <c r="F21" t="n">
-        <v>362</v>
-      </c>
-      <c r="G21" t="n">
-        <v>373.69</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
+      <c r="M21" t="n">
+        <v>1.075</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:09.273</t>
+          <t>2026-05-29 09:44:50.786</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1779505024914</v>
+        <v>1780022689805</v>
       </c>
       <c r="C22" t="n">
-        <v>92634</v>
+        <v>82297</v>
       </c>
       <c r="D22" t="n">
-        <v>-158.27</v>
+        <v>315.56</v>
       </c>
       <c r="E22" t="n">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="F22" t="n">
-        <v>2334</v>
+        <v>760</v>
       </c>
       <c r="G22" t="n">
-        <v>373.69</v>
+        <v>339.7</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I22" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J22" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K22" t="n">
+        <v>980</v>
+      </c>
+      <c r="L22" t="n">
+        <v>117</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.079</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:09.548</t>
+          <t>2026-05-29 09:44:50.787</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1779505025115</v>
+        <v>1780022690024</v>
       </c>
       <c r="C23" t="n">
-        <v>92396</v>
+        <v>83782</v>
       </c>
       <c r="D23" t="n">
-        <v>-388.35</v>
+        <v>1784.78</v>
       </c>
       <c r="E23" t="n">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="F23" t="n">
-        <v>2334</v>
+        <v>760</v>
       </c>
       <c r="G23" t="n">
-        <v>373.69</v>
+        <v>339.7</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I23" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J23" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K23" t="n">
+        <v>762</v>
+      </c>
+      <c r="L23" t="n">
+        <v>105</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.854</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:09.549</t>
+          <t>2026-05-29 09:44:51.853</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1779505025317</v>
+        <v>1780022690224</v>
       </c>
       <c r="C24" t="n">
-        <v>92409</v>
+        <v>83311</v>
       </c>
       <c r="D24" t="n">
-        <v>-355.94</v>
+        <v>1224.54</v>
       </c>
       <c r="E24" t="n">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="F24" t="n">
-        <v>2334</v>
+        <v>760</v>
       </c>
       <c r="G24" t="n">
-        <v>373.69</v>
+        <v>339.7</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I24" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J24" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1627</v>
+      </c>
+      <c r="L24" t="n">
+        <v>114</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.97</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:09.923</t>
+          <t>2026-05-29 09:44:51.855</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1779505025518</v>
+        <v>1780022690424</v>
       </c>
       <c r="C25" t="n">
-        <v>92390</v>
+        <v>82678</v>
       </c>
       <c r="D25" t="n">
-        <v>-357.14</v>
+        <v>530.3200000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="F25" t="n">
-        <v>2334</v>
+        <v>760</v>
       </c>
       <c r="G25" t="n">
-        <v>373.69</v>
+        <v>339.7</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I25" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J25" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1429</v>
+      </c>
+      <c r="L25" t="n">
+        <v>106</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.657</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:09.933</t>
+          <t>2026-05-29 09:44:51.856</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1779505025719</v>
+        <v>1780022690624</v>
       </c>
       <c r="C26" t="n">
-        <v>94040</v>
+        <v>83551</v>
       </c>
       <c r="D26" t="n">
-        <v>1310.72</v>
+        <v>1376.8</v>
       </c>
       <c r="E26" t="n">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="F26" t="n">
-        <v>745</v>
+        <v>760</v>
       </c>
       <c r="G26" t="n">
-        <v>367.47</v>
+        <v>339.7</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I26" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J26" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1231</v>
+      </c>
+      <c r="L26" t="n">
+        <v>106</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.773</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:10.626</t>
+          <t>2026-05-29 09:44:51.856</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1779505025920</v>
+        <v>1780022690824</v>
       </c>
       <c r="C27" t="n">
-        <v>93294</v>
+        <v>84266</v>
       </c>
       <c r="D27" t="n">
-        <v>499.18</v>
+        <v>2022.96</v>
       </c>
       <c r="E27" t="n">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="F27" t="n">
-        <v>745</v>
+        <v>760</v>
       </c>
       <c r="G27" t="n">
-        <v>367.47</v>
+        <v>339.7</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I27" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J27" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1032</v>
+      </c>
+      <c r="L27" t="n">
+        <v>106</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.544</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:11.004</t>
+          <t>2026-05-29 09:44:52.863</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1779505026122</v>
+        <v>1780022691024</v>
       </c>
       <c r="C28" t="n">
-        <v>92781</v>
+        <v>84449</v>
       </c>
       <c r="D28" t="n">
-        <v>-38.78</v>
+        <v>2104.81</v>
       </c>
       <c r="E28" t="n">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="F28" t="n">
-        <v>745</v>
+        <v>760</v>
       </c>
       <c r="G28" t="n">
-        <v>367.47</v>
+        <v>339.7</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I28" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J28" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1838</v>
+      </c>
+      <c r="L28" t="n">
+        <v>112</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.662</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:11.005</t>
+          <t>2026-05-29 09:44:52.940</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1779505026323</v>
+        <v>1780022691224</v>
       </c>
       <c r="C29" t="n">
-        <v>92841</v>
+        <v>84302</v>
       </c>
       <c r="D29" t="n">
-        <v>23.16</v>
+        <v>1852.57</v>
       </c>
       <c r="E29" t="n">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="F29" t="n">
-        <v>745</v>
+        <v>760</v>
       </c>
       <c r="G29" t="n">
-        <v>367.47</v>
+        <v>339.7</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I29" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J29" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1715</v>
+      </c>
+      <c r="L29" t="n">
+        <v>109</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.009</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:11.005</t>
+          <t>2026-05-29 09:44:52.941</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1779505026524</v>
+        <v>1780022691443</v>
       </c>
       <c r="C30" t="n">
-        <v>92636</v>
+        <v>83468</v>
       </c>
       <c r="D30" t="n">
-        <v>-183</v>
+        <v>925.9400000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="F30" t="n">
-        <v>745</v>
+        <v>760</v>
       </c>
       <c r="G30" t="n">
-        <v>367.47</v>
+        <v>339.7</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I30" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J30" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1497</v>
+      </c>
+      <c r="L30" t="n">
+        <v>107</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.045</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:11.006</t>
+          <t>2026-05-29 09:44:53.414</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1779505026725</v>
+        <v>1780022691643</v>
       </c>
       <c r="C31" t="n">
-        <v>92570</v>
+        <v>83257</v>
       </c>
       <c r="D31" t="n">
-        <v>-239.85</v>
+        <v>668.65</v>
       </c>
       <c r="E31" t="n">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="F31" t="n">
-        <v>745</v>
+        <v>760</v>
       </c>
       <c r="G31" t="n">
-        <v>367.47</v>
+        <v>339.7</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I31" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J31" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1770</v>
+      </c>
+      <c r="L31" t="n">
+        <v>107</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.27</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:11.309</t>
+          <t>2026-05-29 09:44:53.415</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1779505026927</v>
+        <v>1780022691843</v>
       </c>
       <c r="C32" t="n">
-        <v>92468</v>
+        <v>83613</v>
       </c>
       <c r="D32" t="n">
-        <v>-329.85</v>
+        <v>991.21</v>
       </c>
       <c r="E32" t="n">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="F32" t="n">
-        <v>745</v>
+        <v>760</v>
       </c>
       <c r="G32" t="n">
-        <v>367.47</v>
+        <v>339.7</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I32" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J32" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1572</v>
+      </c>
+      <c r="L32" t="n">
+        <v>104</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.928</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:11.325</t>
+          <t>2026-05-29 09:44:53.416</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1779505027128</v>
+        <v>1780022692043</v>
       </c>
       <c r="C33" t="n">
-        <v>92947</v>
+        <v>84078</v>
       </c>
       <c r="D33" t="n">
-        <v>165.64</v>
+        <v>1406.65</v>
       </c>
       <c r="E33" t="n">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="F33" t="n">
-        <v>745</v>
+        <v>760</v>
       </c>
       <c r="G33" t="n">
-        <v>367.47</v>
+        <v>339.7</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I33" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J33" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1373</v>
+      </c>
+      <c r="L33" t="n">
+        <v>105</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.821</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:12.168</t>
+          <t>2026-05-29 09:44:53.417</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1779505027329</v>
+        <v>1780022692243</v>
       </c>
       <c r="C34" t="n">
-        <v>93030</v>
+        <v>84425</v>
       </c>
       <c r="D34" t="n">
-        <v>240.36</v>
+        <v>1683.32</v>
       </c>
       <c r="E34" t="n">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="F34" t="n">
-        <v>745</v>
+        <v>760</v>
       </c>
       <c r="G34" t="n">
-        <v>367.47</v>
+        <v>339.7</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I34" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J34" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1174</v>
+      </c>
+      <c r="L34" t="n">
+        <v>104</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.74</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:12.512</t>
+          <t>2026-05-29 09:44:53.644</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1779505027530</v>
+        <v>1780022692443</v>
       </c>
       <c r="C35" t="n">
-        <v>92816</v>
+        <v>84259</v>
       </c>
       <c r="D35" t="n">
-        <v>14.34</v>
+        <v>1433.15</v>
       </c>
       <c r="E35" t="n">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="F35" t="n">
-        <v>745</v>
+        <v>760</v>
       </c>
       <c r="G35" t="n">
-        <v>367.47</v>
+        <v>339.7</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I35" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J35" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1199</v>
+      </c>
+      <c r="L35" t="n">
+        <v>105</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.159</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:12.849</t>
+          <t>2026-05-29 09:44:53.645</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1779505027731</v>
+        <v>1780022692643</v>
       </c>
       <c r="C36" t="n">
-        <v>93053</v>
+        <v>84758</v>
       </c>
       <c r="D36" t="n">
-        <v>250.62</v>
+        <v>1860.5</v>
       </c>
       <c r="E36" t="n">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="F36" t="n">
-        <v>745</v>
+        <v>760</v>
       </c>
       <c r="G36" t="n">
-        <v>367.47</v>
+        <v>339.7</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I36" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J36" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1001</v>
+      </c>
+      <c r="L36" t="n">
+        <v>115</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.871</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:12.851</t>
+          <t>2026-05-29 09:44:53.646</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1779505027933</v>
+        <v>1780022692862</v>
       </c>
       <c r="C37" t="n">
-        <v>92929</v>
+        <v>85660</v>
       </c>
       <c r="D37" t="n">
-        <v>114.09</v>
+        <v>2669.47</v>
       </c>
       <c r="E37" t="n">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="F37" t="n">
-        <v>2113</v>
+        <v>760</v>
       </c>
       <c r="G37" t="n">
-        <v>367.47</v>
+        <v>339.7</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I37" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J37" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K37" t="n">
+        <v>783</v>
+      </c>
+      <c r="L37" t="n">
+        <v>110</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.86</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:12.852</t>
+          <t>2026-05-29 09:44:54.540</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1779505028134</v>
+        <v>1780022693062</v>
       </c>
       <c r="C38" t="n">
-        <v>93036</v>
+        <v>83921</v>
       </c>
       <c r="D38" t="n">
-        <v>215.39</v>
+        <v>797</v>
       </c>
       <c r="E38" t="n">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="F38" t="n">
-        <v>2113</v>
+        <v>760</v>
       </c>
       <c r="G38" t="n">
-        <v>367.47</v>
+        <v>339.7</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I38" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J38" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1476</v>
+      </c>
+      <c r="L38" t="n">
+        <v>115</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.517</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:12.854</t>
+          <t>2026-05-29 09:44:54.562</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1779505028335</v>
+        <v>1780022693262</v>
       </c>
       <c r="C39" t="n">
-        <v>93018</v>
+        <v>81709</v>
       </c>
       <c r="D39" t="n">
-        <v>186.62</v>
+        <v>-1454.85</v>
       </c>
       <c r="E39" t="n">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="F39" t="n">
-        <v>2113</v>
+        <v>760</v>
       </c>
       <c r="G39" t="n">
-        <v>367.47</v>
+        <v>339.7</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I39" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J39" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1299</v>
+      </c>
+      <c r="L39" t="n">
+        <v>105</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.461</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:13.135</t>
+          <t>2026-05-29 09:44:54.766</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1779505028536</v>
+        <v>1780022693462</v>
       </c>
       <c r="C40" t="n">
-        <v>93167</v>
+        <v>82717</v>
       </c>
       <c r="D40" t="n">
-        <v>326.29</v>
+        <v>-374.11</v>
       </c>
       <c r="E40" t="n">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="F40" t="n">
-        <v>2113</v>
+        <v>760</v>
       </c>
       <c r="G40" t="n">
-        <v>367.47</v>
+        <v>339.7</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I40" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J40" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1303</v>
+      </c>
+      <c r="L40" t="n">
+        <v>110</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.743</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:13.222</t>
+          <t>2026-05-29 09:44:54.812</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1779505028738</v>
+        <v>1780022693662</v>
       </c>
       <c r="C41" t="n">
-        <v>93397</v>
+        <v>82608</v>
       </c>
       <c r="D41" t="n">
-        <v>539.97</v>
+        <v>-464.4</v>
       </c>
       <c r="E41" t="n">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="F41" t="n">
-        <v>2113</v>
+        <v>760</v>
       </c>
       <c r="G41" t="n">
-        <v>367.47</v>
+        <v>339.7</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I41" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J41" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1149</v>
+      </c>
+      <c r="L41" t="n">
+        <v>106</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.537</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:13.485</t>
+          <t>2026-05-29 09:44:54.827</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1779505028939</v>
+        <v>1780022693862</v>
       </c>
       <c r="C42" t="n">
-        <v>93087</v>
+        <v>82937</v>
       </c>
       <c r="D42" t="n">
-        <v>202.97</v>
+        <v>-112.18</v>
       </c>
       <c r="E42" t="n">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="F42" t="n">
-        <v>2113</v>
+        <v>760</v>
       </c>
       <c r="G42" t="n">
-        <v>367.47</v>
+        <v>339.7</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I42" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J42" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K42" t="n">
+        <v>964</v>
+      </c>
+      <c r="L42" t="n">
+        <v>108</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.832</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:13.510</t>
+          <t>2026-05-29 09:44:55.290</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1779505029140</v>
+        <v>1780022694062</v>
       </c>
       <c r="C43" t="n">
-        <v>93233</v>
+        <v>82551</v>
       </c>
       <c r="D43" t="n">
-        <v>338.82</v>
+        <v>-492.57</v>
       </c>
       <c r="E43" t="n">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="F43" t="n">
-        <v>2113</v>
+        <v>760</v>
       </c>
       <c r="G43" t="n">
-        <v>367.47</v>
+        <v>339.7</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I43" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J43" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1227</v>
+      </c>
+      <c r="L43" t="n">
+        <v>114</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.984</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:13.913</t>
+          <t>2026-05-29 09:44:55.291</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1779505029341</v>
+        <v>1780022694281</v>
       </c>
       <c r="C44" t="n">
-        <v>93353</v>
+        <v>83567</v>
       </c>
       <c r="D44" t="n">
-        <v>441.88</v>
+        <v>548.05</v>
       </c>
       <c r="E44" t="n">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="F44" t="n">
-        <v>2113</v>
+        <v>760</v>
       </c>
       <c r="G44" t="n">
-        <v>367.47</v>
+        <v>339.7</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I44" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J44" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1010</v>
+      </c>
+      <c r="L44" t="n">
+        <v>104</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.555</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:13.915</t>
+          <t>2026-05-29 09:44:56.215</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1779505029543</v>
+        <v>1780022694481</v>
       </c>
       <c r="C45" t="n">
-        <v>93045</v>
+        <v>83354</v>
       </c>
       <c r="D45" t="n">
-        <v>111.79</v>
+        <v>307.65</v>
       </c>
       <c r="E45" t="n">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="F45" t="n">
-        <v>1589</v>
+        <v>760</v>
       </c>
       <c r="G45" t="n">
-        <v>367.47</v>
+        <v>339.7</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I45" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J45" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1733</v>
+      </c>
+      <c r="L45" t="n">
+        <v>116</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.83</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:14.262</t>
+          <t>2026-05-29 09:44:56.268</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1779505029744</v>
+        <v>1780022694681</v>
       </c>
       <c r="C46" t="n">
-        <v>93026</v>
+        <v>82460</v>
       </c>
       <c r="D46" t="n">
-        <v>87.2</v>
+        <v>-601.73</v>
       </c>
       <c r="E46" t="n">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="F46" t="n">
-        <v>1589</v>
+        <v>760</v>
       </c>
       <c r="G46" t="n">
-        <v>367.47</v>
+        <v>339.7</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I46" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J46" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1587</v>
+      </c>
+      <c r="L46" t="n">
+        <v>106</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.529</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:14.334</t>
+          <t>2026-05-29 09:44:56.543</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1779505029945</v>
+        <v>1780022694881</v>
       </c>
       <c r="C47" t="n">
-        <v>92869</v>
+        <v>83203</v>
       </c>
       <c r="D47" t="n">
-        <v>-74.16</v>
+        <v>171.36</v>
       </c>
       <c r="E47" t="n">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="F47" t="n">
-        <v>1589</v>
+        <v>760</v>
       </c>
       <c r="G47" t="n">
-        <v>367.47</v>
+        <v>339.7</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I47" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J47" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1662</v>
+      </c>
+      <c r="L47" t="n">
+        <v>118</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.855</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:14.677</t>
+          <t>2026-05-29 09:44:56.544</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1779505030146</v>
+        <v>1780022695081</v>
       </c>
       <c r="C48" t="n">
-        <v>92641</v>
+        <v>84504</v>
       </c>
       <c r="D48" t="n">
-        <v>-298.45</v>
+        <v>1463.79</v>
       </c>
       <c r="E48" t="n">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="F48" t="n">
-        <v>1589</v>
+        <v>760</v>
       </c>
       <c r="G48" t="n">
-        <v>367.47</v>
+        <v>339.7</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I48" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J48" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1463</v>
+      </c>
+      <c r="L48" t="n">
+        <v>114</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.642</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:14.679</t>
+          <t>2026-05-29 09:44:56.545</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1779505030348</v>
+        <v>1780022695281</v>
       </c>
       <c r="C49" t="n">
-        <v>93101</v>
+        <v>82505</v>
       </c>
       <c r="D49" t="n">
-        <v>176.47</v>
+        <v>-608.4</v>
       </c>
       <c r="E49" t="n">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="F49" t="n">
-        <v>1589</v>
+        <v>760</v>
       </c>
       <c r="G49" t="n">
-        <v>367.47</v>
+        <v>339.7</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I49" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J49" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1263</v>
+      </c>
+      <c r="L49" t="n">
+        <v>106</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.615</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:15.022</t>
+          <t>2026-05-29 09:44:56.546</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1779505030549</v>
+        <v>1780022695481</v>
       </c>
       <c r="C50" t="n">
-        <v>93098</v>
+        <v>81751</v>
       </c>
       <c r="D50" t="n">
-        <v>164.65</v>
+        <v>-1331.98</v>
       </c>
       <c r="E50" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F50" t="n">
-        <v>1168</v>
+        <v>760</v>
       </c>
       <c r="G50" t="n">
-        <v>325.17</v>
+        <v>339.7</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I50" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J50" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1064</v>
+      </c>
+      <c r="L50" t="n">
+        <v>105</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.648</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:15.053</t>
+          <t>2026-05-29 09:44:56.996</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1779505030750</v>
+        <v>1780022695700</v>
       </c>
       <c r="C51" t="n">
-        <v>93041</v>
+        <v>81856</v>
       </c>
       <c r="D51" t="n">
-        <v>99.41</v>
+        <v>-1160.38</v>
       </c>
       <c r="E51" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F51" t="n">
-        <v>1168</v>
+        <v>760</v>
       </c>
       <c r="G51" t="n">
-        <v>325.17</v>
+        <v>339.7</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I51" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J51" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1295</v>
+      </c>
+      <c r="L51" t="n">
+        <v>104</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1.16</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:15.849</t>
+          <t>2026-05-29 09:44:57.457</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1779505030951</v>
+        <v>1780022695900</v>
       </c>
       <c r="C52" t="n">
-        <v>92415</v>
+        <v>82464</v>
       </c>
       <c r="D52" t="n">
-        <v>-531.5599999999999</v>
+        <v>-494.36</v>
       </c>
       <c r="E52" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F52" t="n">
-        <v>1168</v>
+        <v>760</v>
       </c>
       <c r="G52" t="n">
-        <v>325.17</v>
+        <v>339.7</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I52" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J52" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K52" t="n">
+        <v>1555</v>
+      </c>
+      <c r="L52" t="n">
+        <v>108</v>
+      </c>
+      <c r="M52" t="n">
+        <v>1.205</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:16.176</t>
+          <t>2026-05-29 09:44:57.458</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1779505031152</v>
+        <v>1780022696100</v>
       </c>
       <c r="C53" t="n">
-        <v>92367</v>
+        <v>83238</v>
       </c>
       <c r="D53" t="n">
-        <v>-552.98</v>
+        <v>304.35</v>
       </c>
       <c r="E53" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F53" t="n">
-        <v>1168</v>
+        <v>760</v>
       </c>
       <c r="G53" t="n">
-        <v>325.17</v>
+        <v>339.7</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I53" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J53" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K53" t="n">
+        <v>1357</v>
+      </c>
+      <c r="L53" t="n">
+        <v>107</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.736</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:16.198</t>
+          <t>2026-05-29 09:44:57.458</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1779505031354</v>
+        <v>1780022696300</v>
       </c>
       <c r="C54" t="n">
-        <v>92552</v>
+        <v>83132</v>
       </c>
       <c r="D54" t="n">
-        <v>-340.33</v>
+        <v>183.14</v>
       </c>
       <c r="E54" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F54" t="n">
-        <v>1168</v>
+        <v>760</v>
       </c>
       <c r="G54" t="n">
-        <v>325.17</v>
+        <v>339.7</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I54" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J54" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1158</v>
+      </c>
+      <c r="L54" t="n">
+        <v>114</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.66</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:16.209</t>
+          <t>2026-05-29 09:44:57.459</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1779505031555</v>
+        <v>1780022696500</v>
       </c>
       <c r="C55" t="n">
-        <v>92412</v>
+        <v>83452</v>
       </c>
       <c r="D55" t="n">
-        <v>-463.31</v>
+        <v>493.98</v>
       </c>
       <c r="E55" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F55" t="n">
-        <v>1168</v>
+        <v>760</v>
       </c>
       <c r="G55" t="n">
-        <v>325.17</v>
+        <v>339.7</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I55" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J55" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K55" t="n">
+        <v>958</v>
+      </c>
+      <c r="L55" t="n">
+        <v>103</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.658</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:16.519</t>
+          <t>2026-05-29 09:44:57.703</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1779505031756</v>
+        <v>1780022696700</v>
       </c>
       <c r="C56" t="n">
-        <v>92609</v>
+        <v>83658</v>
       </c>
       <c r="D56" t="n">
-        <v>-243.15</v>
+        <v>675.28</v>
       </c>
       <c r="E56" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F56" t="n">
-        <v>1168</v>
+        <v>760</v>
       </c>
       <c r="G56" t="n">
-        <v>325.17</v>
+        <v>339.7</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I56" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J56" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K56" t="n">
+        <v>1002</v>
+      </c>
+      <c r="L56" t="n">
+        <v>110</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.964</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:16.521</t>
+          <t>2026-05-29 09:44:57.968</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1779505031957</v>
+        <v>1780022696900</v>
       </c>
       <c r="C57" t="n">
-        <v>92755</v>
+        <v>84067</v>
       </c>
       <c r="D57" t="n">
-        <v>-84.98999999999999</v>
+        <v>1050.52</v>
       </c>
       <c r="E57" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="F57" t="n">
-        <v>1348</v>
+        <v>760</v>
       </c>
       <c r="G57" t="n">
-        <v>371.15</v>
+        <v>339.7</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I57" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J57" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K57" t="n">
+        <v>1067</v>
+      </c>
+      <c r="L57" t="n">
+        <v>112</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.86</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:17.000</t>
+          <t>2026-05-29 09:44:57.968</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1779505032159</v>
+        <v>1780022697119</v>
       </c>
       <c r="C58" t="n">
-        <v>92701</v>
+        <v>83536</v>
       </c>
       <c r="D58" t="n">
-        <v>-134.74</v>
+        <v>466.99</v>
       </c>
       <c r="E58" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="F58" t="n">
-        <v>1348</v>
+        <v>760</v>
       </c>
       <c r="G58" t="n">
-        <v>371.15</v>
+        <v>339.7</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I58" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J58" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K58" t="n">
+        <v>849</v>
+      </c>
+      <c r="L58" t="n">
+        <v>105</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.494</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:17.044</t>
+          <t>2026-05-29 09:44:58.584</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1779505032360</v>
+        <v>1780022697319</v>
       </c>
       <c r="C59" t="n">
-        <v>92925</v>
+        <v>83673</v>
       </c>
       <c r="D59" t="n">
-        <v>96</v>
+        <v>580.64</v>
       </c>
       <c r="E59" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="F59" t="n">
-        <v>1348</v>
+        <v>10732</v>
       </c>
       <c r="G59" t="n">
-        <v>371.15</v>
+        <v>339.7</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I59" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J59" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K59" t="n">
+        <v>1264</v>
+      </c>
+      <c r="L59" t="n">
+        <v>125</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1.262</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:17.173</t>
+          <t>2026-05-29 09:44:58.585</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1779505032561</v>
+        <v>1780022697519</v>
       </c>
       <c r="C60" t="n">
-        <v>93089</v>
+        <v>84569</v>
       </c>
       <c r="D60" t="n">
-        <v>255.2</v>
+        <v>1447.61</v>
       </c>
       <c r="E60" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="F60" t="n">
-        <v>1348</v>
+        <v>10732</v>
       </c>
       <c r="G60" t="n">
-        <v>371.15</v>
+        <v>339.7</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I60" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J60" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1065</v>
+      </c>
+      <c r="L60" t="n">
+        <v>120</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.89</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:17.174</t>
+          <t>2026-05-29 09:44:59.017</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1779505032762</v>
+        <v>1780022697719</v>
       </c>
       <c r="C61" t="n">
-        <v>93035</v>
+        <v>84801</v>
       </c>
       <c r="D61" t="n">
-        <v>188.44</v>
+        <v>1607.23</v>
       </c>
       <c r="E61" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="F61" t="n">
-        <v>1348</v>
+        <v>10732</v>
       </c>
       <c r="G61" t="n">
-        <v>371.15</v>
+        <v>339.7</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I61" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J61" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1296</v>
+      </c>
+      <c r="L61" t="n">
+        <v>114</v>
+      </c>
+      <c r="M61" t="n">
+        <v>1.456</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:18.176</t>
+          <t>2026-05-29 09:44:59.055</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1779505032964</v>
+        <v>1780022697919</v>
       </c>
       <c r="C62" t="n">
-        <v>92899</v>
+        <v>84692</v>
       </c>
       <c r="D62" t="n">
-        <v>43.01</v>
+        <v>1417.87</v>
       </c>
       <c r="E62" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="F62" t="n">
-        <v>1348</v>
+        <v>10732</v>
       </c>
       <c r="G62" t="n">
-        <v>371.15</v>
+        <v>339.7</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I62" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J62" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K62" t="n">
+        <v>1135</v>
+      </c>
+      <c r="L62" t="n">
+        <v>114</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.576</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:18.181</t>
+          <t>2026-05-29 09:44:59.056</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1779505033165</v>
+        <v>1780022698119</v>
       </c>
       <c r="C63" t="n">
-        <v>93464</v>
+        <v>85646</v>
       </c>
       <c r="D63" t="n">
-        <v>605.86</v>
+        <v>2300.97</v>
       </c>
       <c r="E63" t="n">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="F63" t="n">
-        <v>1248</v>
+        <v>10732</v>
       </c>
       <c r="G63" t="n">
-        <v>396.12</v>
+        <v>339.7</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I63" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J63" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K63" t="n">
+        <v>936</v>
+      </c>
+      <c r="L63" t="n">
+        <v>117</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0.575</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:18.501</t>
+          <t>2026-05-29 09:44:59.685</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1779505033366</v>
+        <v>1780022698320</v>
       </c>
       <c r="C64" t="n">
-        <v>92832</v>
+        <v>85992</v>
       </c>
       <c r="D64" t="n">
-        <v>-56.43</v>
+        <v>2531.93</v>
       </c>
       <c r="E64" t="n">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="F64" t="n">
-        <v>1248</v>
+        <v>10732</v>
       </c>
       <c r="G64" t="n">
-        <v>396.12</v>
+        <v>339.7</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I64" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J64" t="n">
+        <v>34.53</v>
+      </c>
+      <c r="K64" t="n">
+        <v>1364</v>
+      </c>
+      <c r="L64" t="n">
+        <v>111</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1.325</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:18.502</t>
+          <t>2026-05-29 09:44:59.687</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1779505033567</v>
+        <v>1780022698519</v>
       </c>
       <c r="C65" t="n">
-        <v>94975</v>
+        <v>85336</v>
       </c>
       <c r="D65" t="n">
-        <v>2089.39</v>
+        <v>1749.33</v>
       </c>
       <c r="E65" t="n">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="F65" t="n">
-        <v>1248</v>
+        <v>10732</v>
       </c>
       <c r="G65" t="n">
-        <v>396.12</v>
+        <v>339.7</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I65" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J65" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K65" t="n">
+        <v>1167</v>
+      </c>
+      <c r="L65" t="n">
+        <v>122</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:18.538</t>
+          <t>2026-05-29 09:44:59.688</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1779505033769</v>
+        <v>1780022698738</v>
       </c>
       <c r="C66" t="n">
-        <v>93245</v>
+        <v>85103</v>
       </c>
       <c r="D66" t="n">
-        <v>254.92</v>
+        <v>1428.86</v>
       </c>
       <c r="E66" t="n">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="F66" t="n">
-        <v>1248</v>
+        <v>10732</v>
       </c>
       <c r="G66" t="n">
-        <v>396.12</v>
+        <v>339.7</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I66" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J66" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K66" t="n">
+        <v>949</v>
+      </c>
+      <c r="L66" t="n">
+        <v>110</v>
+      </c>
+      <c r="M66" t="n">
+        <v>1.088</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:18.566</t>
+          <t>2026-05-29 09:45:00.013</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1779505033970</v>
+        <v>1780022698938</v>
       </c>
       <c r="C67" t="n">
-        <v>92443</v>
+        <v>83727</v>
       </c>
       <c r="D67" t="n">
-        <v>-559.8200000000001</v>
+        <v>-18.58</v>
       </c>
       <c r="E67" t="n">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="F67" t="n">
-        <v>1248</v>
+        <v>10732</v>
       </c>
       <c r="G67" t="n">
-        <v>396.12</v>
+        <v>339.7</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I67" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J67" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K67" t="n">
+        <v>1074</v>
+      </c>
+      <c r="L67" t="n">
+        <v>120</v>
+      </c>
+      <c r="M67" t="n">
+        <v>1.058</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:18.828</t>
+          <t>2026-05-29 09:45:00.015</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1779505034171</v>
+        <v>1780022699138</v>
       </c>
       <c r="C68" t="n">
-        <v>92991</v>
+        <v>82155</v>
       </c>
       <c r="D68" t="n">
-        <v>16.17</v>
+        <v>-1589.65</v>
       </c>
       <c r="E68" t="n">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="F68" t="n">
-        <v>1248</v>
+        <v>10732</v>
       </c>
       <c r="G68" t="n">
-        <v>396.12</v>
+        <v>339.7</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I68" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J68" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K68" t="n">
+        <v>876</v>
+      </c>
+      <c r="L68" t="n">
+        <v>119</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.995</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:18.909</t>
+          <t>2026-05-29 09:45:00.434</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1779505034372</v>
+        <v>1780022699338</v>
       </c>
       <c r="C69" t="n">
-        <v>93336</v>
+        <v>83376</v>
       </c>
       <c r="D69" t="n">
-        <v>360.36</v>
+        <v>-289.17</v>
       </c>
       <c r="E69" t="n">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="F69" t="n">
-        <v>1248</v>
+        <v>10732</v>
       </c>
       <c r="G69" t="n">
-        <v>396.12</v>
+        <v>339.7</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I69" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J69" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K69" t="n">
+        <v>1094</v>
+      </c>
+      <c r="L69" t="n">
+        <v>132</v>
+      </c>
+      <c r="M69" t="n">
+        <v>1.793</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:19.185</t>
+          <t>2026-05-29 09:45:00.435</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1779505034574</v>
+        <v>1780022699538</v>
       </c>
       <c r="C70" t="n">
-        <v>93094</v>
+        <v>82750</v>
       </c>
       <c r="D70" t="n">
-        <v>100.34</v>
+        <v>-900.71</v>
       </c>
       <c r="E70" t="n">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="F70" t="n">
-        <v>1248</v>
+        <v>10732</v>
       </c>
       <c r="G70" t="n">
-        <v>396.12</v>
+        <v>339.7</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I70" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J70" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K70" t="n">
+        <v>896</v>
+      </c>
+      <c r="L70" t="n">
+        <v>122</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.949</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:19.188</t>
+          <t>2026-05-29 09:45:00.900</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1779505034775</v>
+        <v>1780022699738</v>
       </c>
       <c r="C71" t="n">
-        <v>93060</v>
+        <v>83112</v>
       </c>
       <c r="D71" t="n">
-        <v>61.32</v>
+        <v>-493.67</v>
       </c>
       <c r="E71" t="n">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="F71" t="n">
-        <v>1248</v>
+        <v>10732</v>
       </c>
       <c r="G71" t="n">
-        <v>396.12</v>
+        <v>339.7</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I71" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J71" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K71" t="n">
+        <v>1161</v>
+      </c>
+      <c r="L71" t="n">
+        <v>125</v>
+      </c>
+      <c r="M71" t="n">
+        <v>1.021</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:19.206</t>
+          <t>2026-05-29 09:45:00.902</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1779505034976</v>
+        <v>1780022699938</v>
       </c>
       <c r="C72" t="n">
-        <v>92577</v>
+        <v>83619</v>
       </c>
       <c r="D72" t="n">
-        <v>-424.74</v>
+        <v>38.01</v>
       </c>
       <c r="E72" t="n">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="F72" t="n">
-        <v>1248</v>
+        <v>10732</v>
       </c>
       <c r="G72" t="n">
-        <v>396.12</v>
+        <v>339.7</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I72" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J72" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K72" t="n">
+        <v>963</v>
+      </c>
+      <c r="L72" t="n">
+        <v>118</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0.907</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:19.501</t>
+          <t>2026-05-29 09:45:01.289</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1779505035177</v>
+        <v>1780022700157</v>
       </c>
       <c r="C73" t="n">
-        <v>92657</v>
+        <v>83323</v>
       </c>
       <c r="D73" t="n">
-        <v>-323.5</v>
+        <v>-259.89</v>
       </c>
       <c r="E73" t="n">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="F73" t="n">
-        <v>1248</v>
+        <v>10732</v>
       </c>
       <c r="G73" t="n">
-        <v>396.12</v>
+        <v>339.7</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I73" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J73" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K73" t="n">
+        <v>1131</v>
+      </c>
+      <c r="L73" t="n">
+        <v>121</v>
+      </c>
+      <c r="M73" t="n">
+        <v>1.471</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:19.503</t>
+          <t>2026-05-29 09:45:01.296</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1779505035379</v>
+        <v>1780022700357</v>
       </c>
       <c r="C74" t="n">
-        <v>92656</v>
+        <v>84022</v>
       </c>
       <c r="D74" t="n">
-        <v>-308.33</v>
+        <v>452.1</v>
       </c>
       <c r="E74" t="n">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="F74" t="n">
-        <v>1248</v>
+        <v>10732</v>
       </c>
       <c r="G74" t="n">
-        <v>396.12</v>
+        <v>339.7</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I74" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J74" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K74" t="n">
+        <v>939</v>
+      </c>
+      <c r="L74" t="n">
+        <v>121</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.5669999999999999</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:19.903</t>
+          <t>2026-05-29 09:45:01.622</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1779505035580</v>
+        <v>1780022700557</v>
       </c>
       <c r="C75" t="n">
-        <v>92577</v>
+        <v>83027</v>
       </c>
       <c r="D75" t="n">
-        <v>-371.91</v>
+        <v>-565.5</v>
       </c>
       <c r="E75" t="n">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="F75" t="n">
-        <v>1248</v>
+        <v>10732</v>
       </c>
       <c r="G75" t="n">
-        <v>396.12</v>
+        <v>339.7</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I75" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J75" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1064</v>
+      </c>
+      <c r="L75" t="n">
+        <v>127</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.828</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:20.223</t>
+          <t>2026-05-29 09:45:01.623</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1779505035781</v>
+        <v>1780022700757</v>
       </c>
       <c r="C76" t="n">
-        <v>92561</v>
+        <v>81759</v>
       </c>
       <c r="D76" t="n">
-        <v>-369.32</v>
+        <v>-1805.23</v>
       </c>
       <c r="E76" t="n">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="F76" t="n">
-        <v>1248</v>
+        <v>10732</v>
       </c>
       <c r="G76" t="n">
-        <v>396.12</v>
+        <v>339.7</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I76" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J76" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K76" t="n">
+        <v>865</v>
+      </c>
+      <c r="L76" t="n">
+        <v>117</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0.755</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:20.224</t>
+          <t>2026-05-29 09:45:02.117</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1779505035982</v>
+        <v>1780022700957</v>
       </c>
       <c r="C77" t="n">
-        <v>92624</v>
+        <v>82429</v>
       </c>
       <c r="D77" t="n">
-        <v>-287.85</v>
+        <v>-1044.97</v>
       </c>
       <c r="E77" t="n">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="F77" t="n">
-        <v>1248</v>
+        <v>10732</v>
       </c>
       <c r="G77" t="n">
-        <v>396.12</v>
+        <v>339.7</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I77" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J77" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K77" t="n">
+        <v>1159</v>
+      </c>
+      <c r="L77" t="n">
+        <v>130</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0.873</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:20.485</t>
+          <t>2026-05-29 09:45:02.118</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1779505036183</v>
+        <v>1780022701157</v>
       </c>
       <c r="C78" t="n">
-        <v>92602</v>
+        <v>83323</v>
       </c>
       <c r="D78" t="n">
-        <v>-295.46</v>
+        <v>-98.72</v>
       </c>
       <c r="E78" t="n">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="F78" t="n">
-        <v>3058</v>
+        <v>10732</v>
       </c>
       <c r="G78" t="n">
-        <v>396.12</v>
+        <v>339.7</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I78" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J78" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K78" t="n">
+        <v>960</v>
+      </c>
+      <c r="L78" t="n">
+        <v>128</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0.784</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:20.486</t>
+          <t>2026-05-29 09:45:02.297</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1779505036385</v>
+        <v>1780022701357</v>
       </c>
       <c r="C79" t="n">
-        <v>92488</v>
+        <v>83635</v>
       </c>
       <c r="D79" t="n">
-        <v>-394.69</v>
+        <v>218.22</v>
       </c>
       <c r="E79" t="n">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="F79" t="n">
-        <v>3058</v>
+        <v>10732</v>
       </c>
       <c r="G79" t="n">
-        <v>396.12</v>
+        <v>339.7</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I79" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J79" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K79" t="n">
+        <v>939</v>
+      </c>
+      <c r="L79" t="n">
+        <v>126</v>
+      </c>
+      <c r="M79" t="n">
+        <v>1.535</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:20.966</t>
+          <t>2026-05-29 09:45:03.064</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1779505036586</v>
+        <v>1780022701558</v>
       </c>
       <c r="C80" t="n">
-        <v>92725</v>
+        <v>84004</v>
       </c>
       <c r="D80" t="n">
-        <v>-137.95</v>
+        <v>576.3099999999999</v>
       </c>
       <c r="E80" t="n">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="F80" t="n">
-        <v>3058</v>
+        <v>10732</v>
       </c>
       <c r="G80" t="n">
-        <v>396.12</v>
+        <v>339.7</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I80" t="n">
+        <v>49.51</v>
+      </c>
+      <c r="J80" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K80" t="n">
+        <v>1505</v>
+      </c>
+      <c r="L80" t="n">
+        <v>110</v>
+      </c>
+      <c r="M80" t="n">
+        <v>1.437</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:21.192</t>
+          <t>2026-05-29 09:45:03.066</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1779505036787</v>
+        <v>1780022701776</v>
       </c>
       <c r="C81" t="n">
-        <v>93186</v>
+        <v>83947</v>
       </c>
       <c r="D81" t="n">
-        <v>329.95</v>
+        <v>490.49</v>
       </c>
       <c r="E81" t="n">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="F81" t="n">
-        <v>483</v>
+        <v>10732</v>
       </c>
       <c r="G81" t="n">
-        <v>411.29</v>
+        <v>339.7</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I81" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J81" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K81" t="n">
+        <v>1289</v>
+      </c>
+      <c r="L81" t="n">
+        <v>126</v>
+      </c>
+      <c r="M81" t="n">
+        <v>1.034</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:21.483</t>
+          <t>2026-05-29 09:45:03.667</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1779505036988</v>
+        <v>1780022701976</v>
       </c>
       <c r="C82" t="n">
-        <v>92817</v>
+        <v>83083</v>
       </c>
       <c r="D82" t="n">
-        <v>-55.55</v>
+        <v>-398.03</v>
       </c>
       <c r="E82" t="n">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="F82" t="n">
-        <v>483</v>
+        <v>10732</v>
       </c>
       <c r="G82" t="n">
-        <v>411.29</v>
+        <v>339.7</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I82" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J82" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K82" t="n">
+        <v>1690</v>
+      </c>
+      <c r="L82" t="n">
+        <v>118</v>
+      </c>
+      <c r="M82" t="n">
+        <v>1.265</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:21.483</t>
+          <t>2026-05-29 09:45:03.682</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1779505037190</v>
+        <v>1780022702176</v>
       </c>
       <c r="C83" t="n">
-        <v>92827</v>
+        <v>82345</v>
       </c>
       <c r="D83" t="n">
-        <v>-42.77</v>
+        <v>-1116.13</v>
       </c>
       <c r="E83" t="n">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="F83" t="n">
-        <v>483</v>
+        <v>10732</v>
       </c>
       <c r="G83" t="n">
-        <v>411.29</v>
+        <v>339.7</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I83" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J83" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K83" t="n">
+        <v>1505</v>
+      </c>
+      <c r="L83" t="n">
+        <v>118</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0.8159999999999999</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:21.953</t>
+          <t>2026-05-29 09:45:03.683</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1779505037391</v>
+        <v>1780022702376</v>
       </c>
       <c r="C84" t="n">
-        <v>92900</v>
+        <v>81882</v>
       </c>
       <c r="D84" t="n">
-        <v>32.36</v>
+        <v>-1523.32</v>
       </c>
       <c r="E84" t="n">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="F84" t="n">
-        <v>483</v>
+        <v>10732</v>
       </c>
       <c r="G84" t="n">
-        <v>411.29</v>
+        <v>339.7</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I84" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J84" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K84" t="n">
+        <v>1306</v>
+      </c>
+      <c r="L84" t="n">
+        <v>109</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0.7</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:21.954</t>
+          <t>2026-05-29 09:45:03.683</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1779505037592</v>
+        <v>1780022702576</v>
       </c>
       <c r="C85" t="n">
-        <v>92856</v>
+        <v>81717</v>
       </c>
       <c r="D85" t="n">
-        <v>-13.25</v>
+        <v>-1612.16</v>
       </c>
       <c r="E85" t="n">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="F85" t="n">
-        <v>805</v>
+        <v>10732</v>
       </c>
       <c r="G85" t="n">
-        <v>399.05</v>
+        <v>339.7</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I85" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J85" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K85" t="n">
+        <v>1107</v>
+      </c>
+      <c r="L85" t="n">
+        <v>119</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0.5669999999999999</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:22.388</t>
+          <t>2026-05-29 09:45:04.007</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1779505037793</v>
+        <v>1780022702777</v>
       </c>
       <c r="C86" t="n">
-        <v>92472</v>
+        <v>83084</v>
       </c>
       <c r="D86" t="n">
-        <v>-396.59</v>
+        <v>-164.55</v>
       </c>
       <c r="E86" t="n">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="F86" t="n">
-        <v>805</v>
+        <v>10732</v>
       </c>
       <c r="G86" t="n">
-        <v>399.05</v>
+        <v>339.7</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I86" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="J86" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K86" t="n">
+        <v>1229</v>
+      </c>
+      <c r="L86" t="n">
+        <v>118</v>
+      </c>
+      <c r="M86" t="n">
+        <v>1.052</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:22.682</t>
+          <t>2026-05-29 09:45:04.008</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1779505037995</v>
+        <v>1780022702976</v>
       </c>
       <c r="C87" t="n">
-        <v>92539</v>
+        <v>83591</v>
       </c>
       <c r="D87" t="n">
-        <v>-309.76</v>
+        <v>350.68</v>
       </c>
       <c r="E87" t="n">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="F87" t="n">
-        <v>805</v>
+        <v>10732</v>
       </c>
       <c r="G87" t="n">
-        <v>399.05</v>
+        <v>339.7</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I87" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J87" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K87" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L87" t="n">
+        <v>126</v>
+      </c>
+      <c r="M87" t="n">
+        <v>1.225</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:22.684</t>
+          <t>2026-05-29 09:45:04.488</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1779505038196</v>
+        <v>1780022703196</v>
       </c>
       <c r="C88" t="n">
-        <v>92600</v>
+        <v>83846</v>
       </c>
       <c r="D88" t="n">
-        <v>-233.27</v>
+        <v>588.14</v>
       </c>
       <c r="E88" t="n">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="F88" t="n">
-        <v>805</v>
+        <v>10732</v>
       </c>
       <c r="G88" t="n">
-        <v>399.05</v>
+        <v>339.7</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I88" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J88" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K88" t="n">
+        <v>1291</v>
+      </c>
+      <c r="L88" t="n">
+        <v>110</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0.671</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:22.998</t>
+          <t>2026-05-29 09:45:04.503</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1779505038397</v>
+        <v>1780022703395</v>
       </c>
       <c r="C89" t="n">
-        <v>92515</v>
+        <v>84326</v>
       </c>
       <c r="D89" t="n">
-        <v>-306.61</v>
+        <v>1038.74</v>
       </c>
       <c r="E89" t="n">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="F89" t="n">
-        <v>805</v>
+        <v>10732</v>
       </c>
       <c r="G89" t="n">
-        <v>399.05</v>
+        <v>339.7</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I89" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J89" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K89" t="n">
+        <v>1107</v>
+      </c>
+      <c r="L89" t="n">
+        <v>110</v>
+      </c>
+      <c r="M89" t="n">
+        <v>1.345</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:22.998</t>
+          <t>2026-05-29 09:45:06.755</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1779505038598</v>
+        <v>1780022703596</v>
       </c>
       <c r="C90" t="n">
-        <v>92380</v>
+        <v>83891</v>
       </c>
       <c r="D90" t="n">
-        <v>-426.28</v>
+        <v>551.8</v>
       </c>
       <c r="E90" t="n">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="F90" t="n">
-        <v>966</v>
+        <v>10732</v>
       </c>
       <c r="G90" t="n">
-        <v>356.78</v>
+        <v>339.7</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I90" t="n">
+        <v>49.56</v>
+      </c>
+      <c r="J90" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K90" t="n">
+        <v>3156</v>
+      </c>
+      <c r="L90" t="n">
+        <v>111</v>
+      </c>
+      <c r="M90" t="n">
+        <v>2.55</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:23.278</t>
+          <t>2026-05-29 09:45:06.758</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1779505038800</v>
+        <v>1780022703795</v>
       </c>
       <c r="C91" t="n">
-        <v>92277</v>
+        <v>83547</v>
       </c>
       <c r="D91" t="n">
-        <v>-507.97</v>
+        <v>180.21</v>
       </c>
       <c r="E91" t="n">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="F91" t="n">
-        <v>966</v>
+        <v>10732</v>
       </c>
       <c r="G91" t="n">
-        <v>356.78</v>
+        <v>339.7</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I91" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J91" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K91" t="n">
+        <v>2960</v>
+      </c>
+      <c r="L91" t="n">
+        <v>115</v>
+      </c>
+      <c r="M91" t="n">
+        <v>2.606</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:23.309</t>
+          <t>2026-05-29 09:45:06.761</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1779505039001</v>
+        <v>1780022703995</v>
       </c>
       <c r="C92" t="n">
-        <v>92305</v>
+        <v>82856</v>
       </c>
       <c r="D92" t="n">
-        <v>-454.57</v>
+        <v>-519.8</v>
       </c>
       <c r="E92" t="n">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="F92" t="n">
-        <v>966</v>
+        <v>10732</v>
       </c>
       <c r="G92" t="n">
-        <v>356.78</v>
+        <v>339.7</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I92" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J92" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K92" t="n">
+        <v>2763</v>
+      </c>
+      <c r="L92" t="n">
+        <v>113</v>
+      </c>
+      <c r="M92" t="n">
+        <v>2.621</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:23.976</t>
+          <t>2026-05-29 09:45:06.762</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1779505039202</v>
+        <v>1780022704195</v>
       </c>
       <c r="C93" t="n">
-        <v>92048</v>
+        <v>82934</v>
       </c>
       <c r="D93" t="n">
-        <v>-688.84</v>
+        <v>-415.81</v>
       </c>
       <c r="E93" t="n">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="F93" t="n">
-        <v>966</v>
+        <v>10732</v>
       </c>
       <c r="G93" t="n">
-        <v>356.78</v>
+        <v>339.7</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I93" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J93" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K93" t="n">
+        <v>2566</v>
+      </c>
+      <c r="L93" t="n">
+        <v>111</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0.951</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-05-23 09:57:24.290</t>
+          <t>2026-05-29 09:45:06.763</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1779505039403</v>
+        <v>1780022704395</v>
       </c>
       <c r="C94" t="n">
-        <v>92081</v>
+        <v>83060</v>
       </c>
       <c r="D94" t="n">
-        <v>-621.4</v>
+        <v>-269.02</v>
       </c>
       <c r="E94" t="n">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="F94" t="n">
-        <v>966</v>
+        <v>10732</v>
       </c>
       <c r="G94" t="n">
-        <v>356.78</v>
+        <v>339.7</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I94" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J94" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K94" t="n">
+        <v>2367</v>
+      </c>
+      <c r="L94" t="n">
+        <v>122</v>
+      </c>
+      <c r="M94" t="n">
+        <v>1.044</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:06.766</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>1780022704614</v>
+      </c>
+      <c r="C95" t="n">
+        <v>82906</v>
+      </c>
+      <c r="D95" t="n">
+        <v>-409.57</v>
+      </c>
+      <c r="E95" t="n">
+        <v>96</v>
+      </c>
+      <c r="F95" t="n">
+        <v>10732</v>
+      </c>
+      <c r="G95" t="n">
+        <v>339.7</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J95" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K95" t="n">
+        <v>2149</v>
+      </c>
+      <c r="L95" t="n">
+        <v>114</v>
+      </c>
+      <c r="M95" t="n">
+        <v>2.083</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:06.767</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>1780022704814</v>
+      </c>
+      <c r="C96" t="n">
+        <v>82906</v>
+      </c>
+      <c r="D96" t="n">
+        <v>-389.09</v>
+      </c>
+      <c r="E96" t="n">
+        <v>96</v>
+      </c>
+      <c r="F96" t="n">
+        <v>10732</v>
+      </c>
+      <c r="G96" t="n">
+        <v>339.7</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J96" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K96" t="n">
+        <v>1952</v>
+      </c>
+      <c r="L96" t="n">
+        <v>107</v>
+      </c>
+      <c r="M96" t="n">
+        <v>1.252</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:06.770</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>1780022705014</v>
+      </c>
+      <c r="C97" t="n">
+        <v>82648</v>
+      </c>
+      <c r="D97" t="n">
+        <v>-627.64</v>
+      </c>
+      <c r="E97" t="n">
+        <v>96</v>
+      </c>
+      <c r="F97" t="n">
+        <v>10732</v>
+      </c>
+      <c r="G97" t="n">
+        <v>339.7</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I97" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J97" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K97" t="n">
+        <v>1754</v>
+      </c>
+      <c r="L97" t="n">
+        <v>132</v>
+      </c>
+      <c r="M97" t="n">
+        <v>1.612</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:07.203</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>1780022705214</v>
+      </c>
+      <c r="C98" t="n">
+        <v>83119</v>
+      </c>
+      <c r="D98" t="n">
+        <v>-125.25</v>
+      </c>
+      <c r="E98" t="n">
+        <v>96</v>
+      </c>
+      <c r="F98" t="n">
+        <v>10732</v>
+      </c>
+      <c r="G98" t="n">
+        <v>339.7</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I98" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J98" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K98" t="n">
+        <v>1988</v>
+      </c>
+      <c r="L98" t="n">
+        <v>111</v>
+      </c>
+      <c r="M98" t="n">
+        <v>1.315</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:07.642</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>1780022705414</v>
+      </c>
+      <c r="C99" t="n">
+        <v>83063</v>
+      </c>
+      <c r="D99" t="n">
+        <v>-174.99</v>
+      </c>
+      <c r="E99" t="n">
+        <v>96</v>
+      </c>
+      <c r="F99" t="n">
+        <v>10732</v>
+      </c>
+      <c r="G99" t="n">
+        <v>339.7</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I99" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J99" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K99" t="n">
+        <v>2227</v>
+      </c>
+      <c r="L99" t="n">
+        <v>124</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0.526</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:07.642</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>1780022706477</v>
+      </c>
+      <c r="C100" t="n">
+        <v>82752</v>
+      </c>
+      <c r="D100" t="n">
+        <v>-477.24</v>
+      </c>
+      <c r="E100" t="n">
+        <v>96</v>
+      </c>
+      <c r="F100" t="n">
+        <v>10732</v>
+      </c>
+      <c r="G100" t="n">
+        <v>339.7</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I100" t="n">
+        <v>43.73</v>
+      </c>
+      <c r="J100" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K100" t="n">
+        <v>1165</v>
+      </c>
+      <c r="L100" t="n">
+        <v>110</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0.516</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:07.644</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>1780022706693</v>
+      </c>
+      <c r="C101" t="n">
+        <v>82725</v>
+      </c>
+      <c r="D101" t="n">
+        <v>-480.38</v>
+      </c>
+      <c r="E101" t="n">
+        <v>96</v>
+      </c>
+      <c r="F101" t="n">
+        <v>10732</v>
+      </c>
+      <c r="G101" t="n">
+        <v>339.7</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I101" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J101" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K101" t="n">
+        <v>950</v>
+      </c>
+      <c r="L101" t="n">
+        <v>128</v>
+      </c>
+      <c r="M101" t="n">
+        <v>1.488</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:08.093</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>1780022706893</v>
+      </c>
+      <c r="C102" t="n">
+        <v>82624</v>
+      </c>
+      <c r="D102" t="n">
+        <v>-557.36</v>
+      </c>
+      <c r="E102" t="n">
+        <v>96</v>
+      </c>
+      <c r="F102" t="n">
+        <v>10732</v>
+      </c>
+      <c r="G102" t="n">
+        <v>339.7</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J102" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K102" t="n">
+        <v>1199</v>
+      </c>
+      <c r="L102" t="n">
+        <v>125</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0.485</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:08.099</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>1780022707093</v>
+      </c>
+      <c r="C103" t="n">
+        <v>82639</v>
+      </c>
+      <c r="D103" t="n">
+        <v>-514.49</v>
+      </c>
+      <c r="E103" t="n">
+        <v>96</v>
+      </c>
+      <c r="F103" t="n">
+        <v>10732</v>
+      </c>
+      <c r="G103" t="n">
+        <v>339.7</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I103" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J103" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K103" t="n">
+        <v>1005</v>
+      </c>
+      <c r="L103" t="n">
+        <v>122</v>
+      </c>
+      <c r="M103" t="n">
+        <v>1.018</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:08.883</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>1780022707294</v>
+      </c>
+      <c r="C104" t="n">
+        <v>82554</v>
+      </c>
+      <c r="D104" t="n">
+        <v>-573.77</v>
+      </c>
+      <c r="E104" t="n">
+        <v>96</v>
+      </c>
+      <c r="F104" t="n">
+        <v>10732</v>
+      </c>
+      <c r="G104" t="n">
+        <v>339.7</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I104" t="n">
+        <v>49.51</v>
+      </c>
+      <c r="J104" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K104" t="n">
+        <v>1587</v>
+      </c>
+      <c r="L104" t="n">
+        <v>110</v>
+      </c>
+      <c r="M104" t="n">
+        <v>1.599</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:08.884</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>1780022707493</v>
+      </c>
+      <c r="C105" t="n">
+        <v>82584</v>
+      </c>
+      <c r="D105" t="n">
+        <v>-515.08</v>
+      </c>
+      <c r="E105" t="n">
+        <v>96</v>
+      </c>
+      <c r="F105" t="n">
+        <v>10732</v>
+      </c>
+      <c r="G105" t="n">
+        <v>339.7</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I105" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="J105" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K105" t="n">
+        <v>1390</v>
+      </c>
+      <c r="L105" t="n">
+        <v>110</v>
+      </c>
+      <c r="M105" t="n">
+        <v>1.171</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:09.357</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>1780022707712</v>
+      </c>
+      <c r="C106" t="n">
+        <v>82864</v>
+      </c>
+      <c r="D106" t="n">
+        <v>-209.33</v>
+      </c>
+      <c r="E106" t="n">
+        <v>96</v>
+      </c>
+      <c r="F106" t="n">
+        <v>10732</v>
+      </c>
+      <c r="G106" t="n">
+        <v>339.7</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I106" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J106" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K106" t="n">
+        <v>1644</v>
+      </c>
+      <c r="L106" t="n">
+        <v>128</v>
+      </c>
+      <c r="M106" t="n">
+        <v>1.206</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:09.358</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>1780022707912</v>
+      </c>
+      <c r="C107" t="n">
+        <v>82838</v>
+      </c>
+      <c r="D107" t="n">
+        <v>-224.86</v>
+      </c>
+      <c r="E107" t="n">
+        <v>96</v>
+      </c>
+      <c r="F107" t="n">
+        <v>10453</v>
+      </c>
+      <c r="G107" t="n">
+        <v>339.7</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I107" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J107" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K107" t="n">
+        <v>1445</v>
+      </c>
+      <c r="L107" t="n">
+        <v>123</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0.762</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:09.359</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>1780022708112</v>
+      </c>
+      <c r="C108" t="n">
+        <v>82816</v>
+      </c>
+      <c r="D108" t="n">
+        <v>-235.62</v>
+      </c>
+      <c r="E108" t="n">
+        <v>96</v>
+      </c>
+      <c r="F108" t="n">
+        <v>10453</v>
+      </c>
+      <c r="G108" t="n">
+        <v>339.7</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I108" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J108" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K108" t="n">
+        <v>1246</v>
+      </c>
+      <c r="L108" t="n">
+        <v>114</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0.906</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:09.361</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>1780022708313</v>
+      </c>
+      <c r="C109" t="n">
+        <v>83059</v>
+      </c>
+      <c r="D109" t="n">
+        <v>19.16</v>
+      </c>
+      <c r="E109" t="n">
+        <v>96</v>
+      </c>
+      <c r="F109" t="n">
+        <v>10453</v>
+      </c>
+      <c r="G109" t="n">
+        <v>339.7</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I109" t="n">
+        <v>49.52</v>
+      </c>
+      <c r="J109" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K109" t="n">
+        <v>1046</v>
+      </c>
+      <c r="L109" t="n">
+        <v>111</v>
+      </c>
+      <c r="M109" t="n">
+        <v>1.571</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:09.605</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>1780022708513</v>
+      </c>
+      <c r="C110" t="n">
+        <v>82888</v>
+      </c>
+      <c r="D110" t="n">
+        <v>-152.79</v>
+      </c>
+      <c r="E110" t="n">
+        <v>96</v>
+      </c>
+      <c r="F110" t="n">
+        <v>10453</v>
+      </c>
+      <c r="G110" t="n">
+        <v>339.7</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I110" t="n">
+        <v>49.53</v>
+      </c>
+      <c r="J110" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K110" t="n">
+        <v>1091</v>
+      </c>
+      <c r="L110" t="n">
+        <v>111</v>
+      </c>
+      <c r="M110" t="n">
+        <v>0.529</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:09.606</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>1780022708712</v>
+      </c>
+      <c r="C111" t="n">
+        <v>82559</v>
+      </c>
+      <c r="D111" t="n">
+        <v>-474.15</v>
+      </c>
+      <c r="E111" t="n">
+        <v>96</v>
+      </c>
+      <c r="F111" t="n">
+        <v>10453</v>
+      </c>
+      <c r="G111" t="n">
+        <v>339.7</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I111" t="n">
+        <v>49.43</v>
+      </c>
+      <c r="J111" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K111" t="n">
+        <v>893</v>
+      </c>
+      <c r="L111" t="n">
+        <v>111</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:09.641</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>1780022708913</v>
+      </c>
+      <c r="C112" t="n">
+        <v>82357</v>
+      </c>
+      <c r="D112" t="n">
+        <v>-652.45</v>
+      </c>
+      <c r="E112" t="n">
+        <v>96</v>
+      </c>
+      <c r="F112" t="n">
+        <v>10453</v>
+      </c>
+      <c r="G112" t="n">
+        <v>339.7</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I112" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="J112" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K112" t="n">
+        <v>727</v>
+      </c>
+      <c r="L112" t="n">
+        <v>110</v>
+      </c>
+      <c r="M112" t="n">
+        <v>1.116</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:10.009</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>1780022709131</v>
+      </c>
+      <c r="C113" t="n">
+        <v>82244</v>
+      </c>
+      <c r="D113" t="n">
+        <v>-732.8200000000001</v>
+      </c>
+      <c r="E113" t="n">
+        <v>96</v>
+      </c>
+      <c r="F113" t="n">
+        <v>10453</v>
+      </c>
+      <c r="G113" t="n">
+        <v>339.7</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I113" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J113" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K113" t="n">
+        <v>877</v>
+      </c>
+      <c r="L113" t="n">
+        <v>112</v>
+      </c>
+      <c r="M113" t="n">
+        <v>1.236</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:10.590</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>1780022709332</v>
+      </c>
+      <c r="C114" t="n">
+        <v>82238</v>
+      </c>
+      <c r="D114" t="n">
+        <v>-702.1799999999999</v>
+      </c>
+      <c r="E114" t="n">
+        <v>96</v>
+      </c>
+      <c r="F114" t="n">
+        <v>10453</v>
+      </c>
+      <c r="G114" t="n">
+        <v>339.7</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I114" t="n">
+        <v>49.54</v>
+      </c>
+      <c r="J114" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K114" t="n">
+        <v>1257</v>
+      </c>
+      <c r="L114" t="n">
+        <v>114</v>
+      </c>
+      <c r="M114" t="n">
+        <v>1.151</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:10.592</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>1780022709531</v>
+      </c>
+      <c r="C115" t="n">
+        <v>82415</v>
+      </c>
+      <c r="D115" t="n">
+        <v>-490.07</v>
+      </c>
+      <c r="E115" t="n">
+        <v>96</v>
+      </c>
+      <c r="F115" t="n">
+        <v>10453</v>
+      </c>
+      <c r="G115" t="n">
+        <v>339.7</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I115" t="n">
+        <v>49.43</v>
+      </c>
+      <c r="J115" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K115" t="n">
+        <v>1060</v>
+      </c>
+      <c r="L115" t="n">
+        <v>111</v>
+      </c>
+      <c r="M115" t="n">
+        <v>1.265</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:10.594</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>1780022709732</v>
+      </c>
+      <c r="C116" t="n">
+        <v>82432</v>
+      </c>
+      <c r="D116" t="n">
+        <v>-448.57</v>
+      </c>
+      <c r="E116" t="n">
+        <v>96</v>
+      </c>
+      <c r="F116" t="n">
+        <v>1919</v>
+      </c>
+      <c r="G116" t="n">
+        <v>339.7</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I116" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="J116" t="n">
+        <v>35.02</v>
+      </c>
+      <c r="K116" t="n">
+        <v>860</v>
+      </c>
+      <c r="L116" t="n">
+        <v>153</v>
+      </c>
+      <c r="M116" t="n">
+        <v>1.397</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:11.128</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>1780022709931</v>
+      </c>
+      <c r="C117" t="n">
+        <v>82075</v>
+      </c>
+      <c r="D117" t="n">
+        <v>-783.14</v>
+      </c>
+      <c r="E117" t="n">
+        <v>96</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1919</v>
+      </c>
+      <c r="G117" t="n">
+        <v>339.7</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I117" t="n">
+        <v>49.47</v>
+      </c>
+      <c r="J117" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K117" t="n">
+        <v>1196</v>
+      </c>
+      <c r="L117" t="n">
+        <v>109</v>
+      </c>
+      <c r="M117" t="n">
+        <v>1.083</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:11.134</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>1780022710131</v>
+      </c>
+      <c r="C118" t="n">
+        <v>82208</v>
+      </c>
+      <c r="D118" t="n">
+        <v>-610.98</v>
+      </c>
+      <c r="E118" t="n">
+        <v>96</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1919</v>
+      </c>
+      <c r="G118" t="n">
+        <v>339.7</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I118" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J118" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K118" t="n">
+        <v>1002</v>
+      </c>
+      <c r="L118" t="n">
+        <v>97</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.984</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:11.515</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>1780022710331</v>
+      </c>
+      <c r="C119" t="n">
+        <v>82327</v>
+      </c>
+      <c r="D119" t="n">
+        <v>-461.44</v>
+      </c>
+      <c r="E119" t="n">
+        <v>96</v>
+      </c>
+      <c r="F119" t="n">
+        <v>1919</v>
+      </c>
+      <c r="G119" t="n">
+        <v>339.7</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I119" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J119" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K119" t="n">
+        <v>1182</v>
+      </c>
+      <c r="L119" t="n">
+        <v>122</v>
+      </c>
+      <c r="M119" t="n">
+        <v>1.669</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:11.524</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>1780022710550</v>
+      </c>
+      <c r="C120" t="n">
+        <v>82187</v>
+      </c>
+      <c r="D120" t="n">
+        <v>-578.36</v>
+      </c>
+      <c r="E120" t="n">
+        <v>82</v>
+      </c>
+      <c r="F120" t="n">
+        <v>719</v>
+      </c>
+      <c r="G120" t="n">
+        <v>332.21</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I120" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J120" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K120" t="n">
+        <v>973</v>
+      </c>
+      <c r="L120" t="n">
+        <v>107</v>
+      </c>
+      <c r="M120" t="n">
+        <v>1.092</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:11.527</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>1780022710750</v>
+      </c>
+      <c r="C121" t="n">
+        <v>82270</v>
+      </c>
+      <c r="D121" t="n">
+        <v>-466.45</v>
+      </c>
+      <c r="E121" t="n">
+        <v>82</v>
+      </c>
+      <c r="F121" t="n">
+        <v>719</v>
+      </c>
+      <c r="G121" t="n">
+        <v>332.21</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="J121" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K121" t="n">
+        <v>775</v>
+      </c>
+      <c r="L121" t="n">
+        <v>104</v>
+      </c>
+      <c r="M121" t="n">
+        <v>2.179</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:11.944</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>1780022710950</v>
+      </c>
+      <c r="C122" t="n">
+        <v>82484</v>
+      </c>
+      <c r="D122" t="n">
+        <v>-229.12</v>
+      </c>
+      <c r="E122" t="n">
+        <v>104</v>
+      </c>
+      <c r="F122" t="n">
+        <v>480</v>
+      </c>
+      <c r="G122" t="n">
+        <v>331.28</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J122" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K122" t="n">
+        <v>992</v>
+      </c>
+      <c r="L122" t="n">
+        <v>120</v>
+      </c>
+      <c r="M122" t="n">
+        <v>1.458</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:11.945</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>1780022711150</v>
+      </c>
+      <c r="C123" t="n">
+        <v>82402</v>
+      </c>
+      <c r="D123" t="n">
+        <v>-299.67</v>
+      </c>
+      <c r="E123" t="n">
+        <v>104</v>
+      </c>
+      <c r="F123" t="n">
+        <v>480</v>
+      </c>
+      <c r="G123" t="n">
+        <v>331.28</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I123" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J123" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K123" t="n">
+        <v>794</v>
+      </c>
+      <c r="L123" t="n">
+        <v>106</v>
+      </c>
+      <c r="M123" t="n">
+        <v>1.148</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:12.387</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>1780022711350</v>
+      </c>
+      <c r="C124" t="n">
+        <v>82337</v>
+      </c>
+      <c r="D124" t="n">
+        <v>-349.68</v>
+      </c>
+      <c r="E124" t="n">
+        <v>104</v>
+      </c>
+      <c r="F124" t="n">
+        <v>480</v>
+      </c>
+      <c r="G124" t="n">
+        <v>331.28</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I124" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J124" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K124" t="n">
+        <v>1036</v>
+      </c>
+      <c r="L124" t="n">
+        <v>110</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.677</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:12.388</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>1780022711550</v>
+      </c>
+      <c r="C125" t="n">
+        <v>82358</v>
+      </c>
+      <c r="D125" t="n">
+        <v>-311.2</v>
+      </c>
+      <c r="E125" t="n">
+        <v>104</v>
+      </c>
+      <c r="F125" t="n">
+        <v>480</v>
+      </c>
+      <c r="G125" t="n">
+        <v>331.28</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I125" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J125" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K125" t="n">
+        <v>838</v>
+      </c>
+      <c r="L125" t="n">
+        <v>114</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.639</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:12.982</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>1780022711750</v>
+      </c>
+      <c r="C126" t="n">
+        <v>82462</v>
+      </c>
+      <c r="D126" t="n">
+        <v>-191.64</v>
+      </c>
+      <c r="E126" t="n">
+        <v>104</v>
+      </c>
+      <c r="F126" t="n">
+        <v>480</v>
+      </c>
+      <c r="G126" t="n">
+        <v>331.28</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I126" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J126" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K126" t="n">
+        <v>1231</v>
+      </c>
+      <c r="L126" t="n">
+        <v>124</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.792</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:12.983</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>1780022711969</v>
+      </c>
+      <c r="C127" t="n">
+        <v>82275</v>
+      </c>
+      <c r="D127" t="n">
+        <v>-369.06</v>
+      </c>
+      <c r="E127" t="n">
+        <v>88</v>
+      </c>
+      <c r="F127" t="n">
+        <v>900</v>
+      </c>
+      <c r="G127" t="n">
+        <v>338.35</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I127" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J127" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K127" t="n">
+        <v>1013</v>
+      </c>
+      <c r="L127" t="n">
+        <v>103</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.8139999999999999</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:13.298</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>1780022712169</v>
+      </c>
+      <c r="C128" t="n">
+        <v>82358</v>
+      </c>
+      <c r="D128" t="n">
+        <v>-267.6</v>
+      </c>
+      <c r="E128" t="n">
+        <v>88</v>
+      </c>
+      <c r="F128" t="n">
+        <v>900</v>
+      </c>
+      <c r="G128" t="n">
+        <v>338.35</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I128" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J128" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K128" t="n">
+        <v>1128</v>
+      </c>
+      <c r="L128" t="n">
+        <v>107</v>
+      </c>
+      <c r="M128" t="n">
+        <v>1.133</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:13.299</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>1780022712369</v>
+      </c>
+      <c r="C129" t="n">
+        <v>82445</v>
+      </c>
+      <c r="D129" t="n">
+        <v>-167.22</v>
+      </c>
+      <c r="E129" t="n">
+        <v>88</v>
+      </c>
+      <c r="F129" t="n">
+        <v>900</v>
+      </c>
+      <c r="G129" t="n">
+        <v>338.35</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I129" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J129" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K129" t="n">
+        <v>929</v>
+      </c>
+      <c r="L129" t="n">
+        <v>105</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.858</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:13.721</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>1780022712569</v>
+      </c>
+      <c r="C130" t="n">
+        <v>82218</v>
+      </c>
+      <c r="D130" t="n">
+        <v>-385.86</v>
+      </c>
+      <c r="E130" t="n">
+        <v>93</v>
+      </c>
+      <c r="F130" t="n">
+        <v>599</v>
+      </c>
+      <c r="G130" t="n">
+        <v>329.14</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I130" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J130" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K130" t="n">
+        <v>1149</v>
+      </c>
+      <c r="L130" t="n">
+        <v>111</v>
+      </c>
+      <c r="M130" t="n">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:13.722</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>1780022712769</v>
+      </c>
+      <c r="C131" t="n">
+        <v>82048</v>
+      </c>
+      <c r="D131" t="n">
+        <v>-536.5700000000001</v>
+      </c>
+      <c r="E131" t="n">
+        <v>93</v>
+      </c>
+      <c r="F131" t="n">
+        <v>599</v>
+      </c>
+      <c r="G131" t="n">
+        <v>329.14</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I131" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J131" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K131" t="n">
+        <v>952</v>
+      </c>
+      <c r="L131" t="n">
+        <v>106</v>
+      </c>
+      <c r="M131" t="n">
+        <v>1.381</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:13.724</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>1780022712969</v>
+      </c>
+      <c r="C132" t="n">
+        <v>82074</v>
+      </c>
+      <c r="D132" t="n">
+        <v>-483.74</v>
+      </c>
+      <c r="E132" t="n">
+        <v>93</v>
+      </c>
+      <c r="F132" t="n">
+        <v>599</v>
+      </c>
+      <c r="G132" t="n">
+        <v>329.14</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I132" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J132" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K132" t="n">
+        <v>754</v>
+      </c>
+      <c r="L132" t="n">
+        <v>104</v>
+      </c>
+      <c r="M132" t="n">
+        <v>1.498</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:14.157</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>1780022713169</v>
+      </c>
+      <c r="C133" t="n">
+        <v>82557</v>
+      </c>
+      <c r="D133" t="n">
+        <v>23.45</v>
+      </c>
+      <c r="E133" t="n">
+        <v>93</v>
+      </c>
+      <c r="F133" t="n">
+        <v>599</v>
+      </c>
+      <c r="G133" t="n">
+        <v>329.14</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I133" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J133" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K133" t="n">
+        <v>986</v>
+      </c>
+      <c r="L133" t="n">
+        <v>108</v>
+      </c>
+      <c r="M133" t="n">
+        <v>1.046</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:14.207</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>1780022713369</v>
+      </c>
+      <c r="C134" t="n">
+        <v>83191</v>
+      </c>
+      <c r="D134" t="n">
+        <v>656.27</v>
+      </c>
+      <c r="E134" t="n">
+        <v>90</v>
+      </c>
+      <c r="F134" t="n">
+        <v>840</v>
+      </c>
+      <c r="G134" t="n">
+        <v>328.32</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I134" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J134" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K134" t="n">
+        <v>836</v>
+      </c>
+      <c r="L134" t="n">
+        <v>105</v>
+      </c>
+      <c r="M134" t="n">
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:14.862</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>1780022713588</v>
+      </c>
+      <c r="C135" t="n">
+        <v>83397</v>
+      </c>
+      <c r="D135" t="n">
+        <v>829.46</v>
+      </c>
+      <c r="E135" t="n">
+        <v>90</v>
+      </c>
+      <c r="F135" t="n">
+        <v>840</v>
+      </c>
+      <c r="G135" t="n">
+        <v>328.32</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I135" t="n">
+        <v>49.47</v>
+      </c>
+      <c r="J135" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K135" t="n">
+        <v>1273</v>
+      </c>
+      <c r="L135" t="n">
+        <v>116</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.925</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:14.864</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>1780022713788</v>
+      </c>
+      <c r="C136" t="n">
+        <v>83878</v>
+      </c>
+      <c r="D136" t="n">
+        <v>1268.99</v>
+      </c>
+      <c r="E136" t="n">
+        <v>90</v>
+      </c>
+      <c r="F136" t="n">
+        <v>840</v>
+      </c>
+      <c r="G136" t="n">
+        <v>328.32</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I136" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J136" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K136" t="n">
+        <v>1075</v>
+      </c>
+      <c r="L136" t="n">
+        <v>109</v>
+      </c>
+      <c r="M136" t="n">
+        <v>1.168</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:15.193</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>1780022713988</v>
+      </c>
+      <c r="C137" t="n">
+        <v>83855</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1182.54</v>
+      </c>
+      <c r="E137" t="n">
+        <v>90</v>
+      </c>
+      <c r="F137" t="n">
+        <v>840</v>
+      </c>
+      <c r="G137" t="n">
+        <v>328.32</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I137" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="J137" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K137" t="n">
+        <v>1203</v>
+      </c>
+      <c r="L137" t="n">
+        <v>123</v>
+      </c>
+      <c r="M137" t="n">
+        <v>1.621</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:15.195</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>1780022714188</v>
+      </c>
+      <c r="C138" t="n">
+        <v>83648</v>
+      </c>
+      <c r="D138" t="n">
+        <v>916.41</v>
+      </c>
+      <c r="E138" t="n">
+        <v>90</v>
+      </c>
+      <c r="F138" t="n">
+        <v>840</v>
+      </c>
+      <c r="G138" t="n">
+        <v>328.32</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I138" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J138" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K138" t="n">
+        <v>1006</v>
+      </c>
+      <c r="L138" t="n">
+        <v>110</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.962</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:15.206</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>1780022714388</v>
+      </c>
+      <c r="C139" t="n">
+        <v>83818</v>
+      </c>
+      <c r="D139" t="n">
+        <v>1040.59</v>
+      </c>
+      <c r="E139" t="n">
+        <v>90</v>
+      </c>
+      <c r="F139" t="n">
+        <v>840</v>
+      </c>
+      <c r="G139" t="n">
+        <v>328.32</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I139" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J139" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K139" t="n">
+        <v>816</v>
+      </c>
+      <c r="L139" t="n">
+        <v>105</v>
+      </c>
+      <c r="M139" t="n">
+        <v>2.18</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:15.562</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>1780022714588</v>
+      </c>
+      <c r="C140" t="n">
+        <v>83206</v>
+      </c>
+      <c r="D140" t="n">
+        <v>376.56</v>
+      </c>
+      <c r="E140" t="n">
+        <v>90</v>
+      </c>
+      <c r="F140" t="n">
+        <v>840</v>
+      </c>
+      <c r="G140" t="n">
+        <v>328.32</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I140" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J140" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K140" t="n">
+        <v>973</v>
+      </c>
+      <c r="L140" t="n">
+        <v>108</v>
+      </c>
+      <c r="M140" t="n">
+        <v>1.408</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:15.592</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>1780022714788</v>
+      </c>
+      <c r="C141" t="n">
+        <v>82994</v>
+      </c>
+      <c r="D141" t="n">
+        <v>145.73</v>
+      </c>
+      <c r="E141" t="n">
+        <v>90</v>
+      </c>
+      <c r="F141" t="n">
+        <v>840</v>
+      </c>
+      <c r="G141" t="n">
+        <v>328.32</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I141" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J141" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K141" t="n">
+        <v>804</v>
+      </c>
+      <c r="L141" t="n">
+        <v>107</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.769</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:16.008</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>1780022714988</v>
+      </c>
+      <c r="C142" t="n">
+        <v>83825</v>
+      </c>
+      <c r="D142" t="n">
+        <v>969.45</v>
+      </c>
+      <c r="E142" t="n">
+        <v>90</v>
+      </c>
+      <c r="F142" t="n">
+        <v>840</v>
+      </c>
+      <c r="G142" t="n">
+        <v>328.32</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I142" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J142" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K142" t="n">
+        <v>1019</v>
+      </c>
+      <c r="L142" t="n">
+        <v>108</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.652</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:16.009</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>1780022715207</v>
+      </c>
+      <c r="C143" t="n">
+        <v>83124</v>
+      </c>
+      <c r="D143" t="n">
+        <v>219.97</v>
+      </c>
+      <c r="E143" t="n">
+        <v>90</v>
+      </c>
+      <c r="F143" t="n">
+        <v>840</v>
+      </c>
+      <c r="G143" t="n">
+        <v>328.32</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I143" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J143" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K143" t="n">
+        <v>801</v>
+      </c>
+      <c r="L143" t="n">
+        <v>105</v>
+      </c>
+      <c r="M143" t="n">
+        <v>1.062</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:16.348</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>1780022715407</v>
+      </c>
+      <c r="C144" t="n">
+        <v>83281</v>
+      </c>
+      <c r="D144" t="n">
+        <v>365.97</v>
+      </c>
+      <c r="E144" t="n">
+        <v>90</v>
+      </c>
+      <c r="F144" t="n">
+        <v>840</v>
+      </c>
+      <c r="G144" t="n">
+        <v>328.32</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I144" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J144" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K144" t="n">
+        <v>939</v>
+      </c>
+      <c r="L144" t="n">
+        <v>108</v>
+      </c>
+      <c r="M144" t="n">
+        <v>1.173</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:16.349</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>1780022715607</v>
+      </c>
+      <c r="C145" t="n">
+        <v>83411</v>
+      </c>
+      <c r="D145" t="n">
+        <v>477.68</v>
+      </c>
+      <c r="E145" t="n">
+        <v>90</v>
+      </c>
+      <c r="F145" t="n">
+        <v>840</v>
+      </c>
+      <c r="G145" t="n">
+        <v>328.32</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I145" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J145" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K145" t="n">
+        <v>741</v>
+      </c>
+      <c r="L145" t="n">
+        <v>113</v>
+      </c>
+      <c r="M145" t="n">
+        <v>1.229</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:16.718</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>1780022715807</v>
+      </c>
+      <c r="C146" t="n">
+        <v>82652</v>
+      </c>
+      <c r="D146" t="n">
+        <v>-305.21</v>
+      </c>
+      <c r="E146" t="n">
+        <v>90</v>
+      </c>
+      <c r="F146" t="n">
+        <v>2538</v>
+      </c>
+      <c r="G146" t="n">
+        <v>328.32</v>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I146" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J146" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K146" t="n">
+        <v>910</v>
+      </c>
+      <c r="L146" t="n">
+        <v>119</v>
+      </c>
+      <c r="M146" t="n">
+        <v>0.965</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:17.082</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>1780022716008</v>
+      </c>
+      <c r="C147" t="n">
+        <v>83397</v>
+      </c>
+      <c r="D147" t="n">
+        <v>455.05</v>
+      </c>
+      <c r="E147" t="n">
+        <v>90</v>
+      </c>
+      <c r="F147" t="n">
+        <v>2538</v>
+      </c>
+      <c r="G147" t="n">
+        <v>328.32</v>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I147" t="n">
+        <v>49.47</v>
+      </c>
+      <c r="J147" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K147" t="n">
+        <v>1072</v>
+      </c>
+      <c r="L147" t="n">
+        <v>107</v>
+      </c>
+      <c r="M147" t="n">
+        <v>1.307</v>
       </c>
     </row>
   </sheetData>
